--- a/game doc/1组 最终版.xlsx
+++ b/game doc/1组 最终版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="860" activeTab="17"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="860" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="初始年财报" sheetId="3" r:id="rId1"/>
@@ -641,13 +641,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="0.0_ "/>
+    <numFmt numFmtId="181" formatCode="0.0%"/>
+    <numFmt numFmtId="182" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -1436,19 +1436,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2026,19 +2026,19 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2050,16 +2050,16 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="17" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2110,22 +2110,22 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="182" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="P10" s="43">
         <f>'3年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -4363,22 +4363,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'3年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -4414,7 +4414,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'3年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -4568,7 +4568,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'3年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -4593,7 +4593,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'3年财报'!G8+O28</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -4616,7 +4616,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -4790,7 +4790,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'3年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -4858,14 +4858,14 @@
       </c>
       <c r="I60" s="157">
         <f>'4年财报'!$C$22/'4年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.0277777777777778</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'4年财报'!$C$22/'4年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.00495049504950495</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="G6" s="10">
         <f>'3年财报'!G6+'4年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G7" s="10">
         <f>'3年财报'!G7+'4年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="K7" s="10">
         <f>'4年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G8" s="10">
         <f>'3年财报'!G8+'4年经营'!G61</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="K8" s="10">
         <f>'4年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'4年经营'!O51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G13" s="10">
         <f>'4年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="K16" s="10">
         <f>'3年财报'!K16+'3年财报'!K17</f>
-        <v>19</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="P10" s="43">
         <f>'4年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -7056,22 +7056,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'4年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -7107,7 +7107,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'4年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -7261,7 +7261,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'4年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -7286,7 +7286,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'4年财报'!G8+O28</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -7309,7 +7309,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -7483,7 +7483,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'4年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -7551,14 +7551,14 @@
       </c>
       <c r="I60" s="157">
         <f>'5年财报'!$C$22/'5年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.0285714285714286</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'5年财报'!$C$22/'5年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.00497512437810945</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="G6" s="10">
         <f>'4年财报'!G6+'5年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="G7" s="10">
         <f>'4年财报'!G7+'5年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="K7" s="10">
         <f>'5年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="G8" s="10">
         <f>'4年财报'!G8+'5年经营'!G61</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="K8" s="10">
         <f>'5年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'5年经营'!O51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="G13" s="10">
         <f>'5年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="K16" s="10">
         <f>'4年财报'!K16+'4年财报'!K17</f>
-        <v>19</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="P10" s="43">
         <f>'5年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -9749,22 +9749,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'5年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -9800,7 +9800,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'5年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -9954,7 +9954,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'5年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -9979,7 +9979,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'5年财报'!G8+O28</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -10002,7 +10002,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -10176,7 +10176,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'5年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -10244,14 +10244,14 @@
       </c>
       <c r="I60" s="157">
         <f>'6年财报'!$C$22/'6年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.0294117647058824</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'6年财报'!$C$22/'6年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="G6" s="10">
         <f>'5年财报'!G6+'6年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G7" s="10">
         <f>'5年财报'!G7+'6年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="K7" s="10">
         <f>'6年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="G8" s="10">
         <f>'5年财报'!G8+'6年经营'!G61</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="K8" s="10">
         <f>'6年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'6年经营'!O51</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="G13" s="10">
         <f>'6年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="K16" s="10">
         <f>'5年财报'!K16+'5年财报'!K17</f>
-        <v>19</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="P10" s="43">
         <f>'6年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -12442,22 +12442,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'6年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -12493,7 +12493,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'6年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -12647,7 +12647,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'6年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -12672,7 +12672,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'6年财报'!G8+O28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -12869,7 +12869,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'6年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -13524,7 +13524,7 @@
       </c>
       <c r="G6" s="10">
         <f>'6年财报'!G6+'7年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="G7" s="10">
         <f>'6年财报'!G7+'7年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="K7" s="10">
         <f>'7年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="G8" s="10">
         <f>'6年财报'!G8+'7年经营'!G61</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="K8" s="10">
         <f>'7年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="G13" s="10">
         <f>'7年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="K16" s="10">
         <f>'6年财报'!K16+'6年财报'!K17</f>
-        <v>19</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="P10" s="43">
         <f>'7年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -15135,22 +15135,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'7年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -15186,7 +15186,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'7年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -15340,7 +15340,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'7年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -15365,7 +15365,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'7年财报'!G8+O28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -15562,7 +15562,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'7年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G6" s="10">
         <f>'7年财报'!G6+'8年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="G7" s="10">
         <f>'7年财报'!G7+'8年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="K7" s="10">
         <f>'8年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="G8" s="10">
         <f>'7年财报'!G8+'8年经营'!G61</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="K8" s="10">
         <f>'8年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="G13" s="10">
         <f>'8年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="K16" s="10">
         <f>'7年财报'!K16+'7年财报'!K17</f>
-        <v>19</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -16668,11 +16668,13 @@
         <v>45</v>
       </c>
       <c r="L2" s="31"/>
-      <c r="M2" s="32"/>
+      <c r="M2" s="32">
+        <v>11</v>
+      </c>
       <c r="N2" s="32"/>
       <c r="O2" s="33">
         <f>P5+O21+O22+O29+O33+O34+O40+O45+O48+O53</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P2" s="34"/>
       <c r="Q2" s="35"/>
@@ -16772,7 +16774,9 @@
       <c r="D5" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="32">
+        <v>11</v>
+      </c>
       <c r="F5" s="32"/>
       <c r="G5" s="32"/>
       <c r="H5" s="32"/>
@@ -16781,15 +16785,16 @@
       <c r="K5" s="32"/>
       <c r="L5" s="32"/>
       <c r="M5" s="40">
-        <f t="shared" ref="M5:M8" si="0">SUM(E5:L5)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N5" s="40"/>
       <c r="O5" s="40">
         <f>SUM(M5:N8)</f>
-        <v>0</v>
-      </c>
-      <c r="P5" s="32"/>
+        <v>11</v>
+      </c>
+      <c r="P5" s="32">
+        <v>1</v>
+      </c>
       <c r="Q5" s="35"/>
       <c r="R5" s="35"/>
       <c r="S5" s="35"/>
@@ -16816,7 +16821,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
       <c r="M6" s="40">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M5:M8" si="0">SUM(E6:L6)</f>
         <v>0</v>
       </c>
       <c r="N6" s="40"/>
@@ -16956,15 +16961,17 @@
       <c r="J10" s="32"/>
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
+      <c r="M10" s="32">
+        <v>20</v>
+      </c>
       <c r="N10" s="32"/>
       <c r="O10" s="40">
         <f>SUM(G10:N10)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P10" s="43">
         <f>初始年财报!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -16991,11 +16998,13 @@
       <c r="J11" s="32"/>
       <c r="K11" s="32"/>
       <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
+      <c r="M11" s="32">
+        <v>2</v>
+      </c>
       <c r="N11" s="32"/>
       <c r="O11" s="40">
         <f t="shared" ref="O11:O12" si="1">SUM(G11:N11)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" s="44"/>
       <c r="Q11" s="35"/>
@@ -17023,11 +17032,13 @@
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
       <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+      <c r="M12" s="32">
+        <v>40</v>
+      </c>
       <c r="N12" s="32"/>
       <c r="O12" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P12" s="46"/>
       <c r="Q12" s="35"/>
@@ -17096,15 +17107,19 @@
       <c r="F14" s="31"/>
       <c r="G14" s="32"/>
       <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
+      <c r="I14" s="32">
+        <v>2</v>
+      </c>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
       <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
+      <c r="M14" s="32">
+        <v>1</v>
+      </c>
       <c r="N14" s="32"/>
       <c r="O14" s="33">
         <f>G14+I14+K14+M14</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="35"/>
@@ -17232,7 +17247,7 @@
       </c>
       <c r="I18" s="33">
         <f>I14+I15+I16+I17</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="34"/>
       <c r="K18" s="33">
@@ -17242,12 +17257,12 @@
       <c r="L18" s="34"/>
       <c r="M18" s="33">
         <f>M14+M15+M16+M17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="34"/>
       <c r="O18" s="33">
         <f>G18+I18+K18+M18</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" s="34"/>
       <c r="Q18" s="35"/>
@@ -17484,17 +17499,25 @@
         <v>79</v>
       </c>
       <c r="F26" s="86"/>
-      <c r="G26" s="32"/>
+      <c r="G26" s="32">
+        <v>6</v>
+      </c>
       <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
+      <c r="I26" s="32">
+        <v>6</v>
+      </c>
       <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="K26" s="32">
+        <v>6</v>
+      </c>
       <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
+      <c r="M26" s="32">
+        <v>6</v>
+      </c>
       <c r="N26" s="32"/>
       <c r="O26" s="40">
         <f t="shared" ref="O26:O28" si="2">SUM(G26:N26)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P26" s="40"/>
     </row>
@@ -17515,11 +17538,13 @@
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
+      <c r="M27" s="32">
+        <v>5</v>
+      </c>
       <c r="N27" s="32"/>
       <c r="O27" s="40">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" s="40"/>
     </row>
@@ -17538,11 +17563,13 @@
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
       <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
+      <c r="M28" s="32">
+        <v>19</v>
+      </c>
       <c r="N28" s="32"/>
       <c r="O28" s="40">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P28" s="40"/>
     </row>
@@ -17557,17 +17584,25 @@
         <v>82</v>
       </c>
       <c r="F29" s="91"/>
-      <c r="G29" s="32"/>
+      <c r="G29" s="32">
+        <v>2</v>
+      </c>
       <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
+      <c r="I29" s="32">
+        <v>1</v>
+      </c>
       <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="K29" s="32">
+        <v>1</v>
+      </c>
       <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
+      <c r="M29" s="32">
+        <v>1</v>
+      </c>
       <c r="N29" s="32"/>
       <c r="O29" s="40">
         <f>SUM(G29:N30)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P29" s="40"/>
     </row>
@@ -17602,15 +17637,19 @@
       <c r="F31" s="36"/>
       <c r="G31" s="32"/>
       <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="I31" s="32">
+        <v>3</v>
+      </c>
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
+      <c r="M31" s="32">
+        <v>1</v>
+      </c>
       <c r="N31" s="32"/>
       <c r="O31" s="40">
         <f>SUM(G31:N32)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" s="40"/>
     </row>
@@ -17643,17 +17682,25 @@
         <v>86</v>
       </c>
       <c r="F33" s="92"/>
-      <c r="G33" s="32"/>
+      <c r="G33" s="32">
+        <v>1</v>
+      </c>
       <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="I33" s="32">
+        <v>1</v>
+      </c>
       <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
+      <c r="K33" s="32">
+        <v>1</v>
+      </c>
       <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
+      <c r="M33" s="32">
+        <v>1</v>
+      </c>
       <c r="N33" s="32"/>
       <c r="O33" s="40">
         <f t="shared" ref="O33:O40" si="3">SUM(G33:N33)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33" s="40"/>
     </row>
@@ -17668,7 +17715,9 @@
         <v>88</v>
       </c>
       <c r="F34" s="92"/>
-      <c r="G34" s="32"/>
+      <c r="G34" s="32">
+        <v>1</v>
+      </c>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -17678,7 +17727,7 @@
       <c r="N34" s="32"/>
       <c r="O34" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="40"/>
     </row>
@@ -17717,13 +17766,15 @@
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
+      <c r="K36" s="32">
+        <v>11</v>
+      </c>
       <c r="L36" s="32"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
       <c r="O36" s="40">
         <f>SUM(G36:N37)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P36" s="40"/>
     </row>
@@ -17756,7 +17807,9 @@
         <v>93</v>
       </c>
       <c r="F38" s="97"/>
-      <c r="G38" s="98"/>
+      <c r="G38" s="98">
+        <v>11</v>
+      </c>
       <c r="H38" s="99"/>
       <c r="I38" s="98"/>
       <c r="J38" s="99"/>
@@ -17766,7 +17819,7 @@
       <c r="N38" s="99"/>
       <c r="O38" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P38" s="40"/>
     </row>
@@ -17779,7 +17832,9 @@
         <v>94</v>
       </c>
       <c r="F39" s="97"/>
-      <c r="G39" s="98"/>
+      <c r="G39" s="98">
+        <v>4</v>
+      </c>
       <c r="H39" s="99"/>
       <c r="I39" s="98"/>
       <c r="J39" s="99"/>
@@ -17789,7 +17844,7 @@
       <c r="N39" s="99"/>
       <c r="O39" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" s="40"/>
     </row>
@@ -17804,17 +17859,25 @@
         <v>96</v>
       </c>
       <c r="F40" s="100"/>
-      <c r="G40" s="32"/>
+      <c r="G40" s="32">
+        <v>1</v>
+      </c>
       <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
+      <c r="I40" s="32">
+        <v>1</v>
+      </c>
       <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
+      <c r="K40" s="32">
+        <v>1</v>
+      </c>
       <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
+      <c r="M40" s="32">
+        <v>1</v>
+      </c>
       <c r="N40" s="32"/>
       <c r="O40" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P40" s="40"/>
     </row>
@@ -17829,22 +17892,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>初始年财报!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="4">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="4"/>
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="4"/>
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -17880,7 +17943,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>初始年财报!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" spans="1:16">
@@ -17924,7 +17987,9 @@
       <c r="L44" s="107"/>
       <c r="M44" s="107"/>
       <c r="N44" s="107"/>
-      <c r="O44" s="108"/>
+      <c r="O44" s="108">
+        <v>140</v>
+      </c>
       <c r="P44" s="46"/>
     </row>
     <row r="45" ht="18.75" spans="1:16">
@@ -17946,7 +18011,9 @@
       <c r="L45" s="107"/>
       <c r="M45" s="107"/>
       <c r="N45" s="107"/>
-      <c r="O45" s="32"/>
+      <c r="O45" s="32">
+        <v>4</v>
+      </c>
       <c r="P45" s="32"/>
     </row>
     <row r="46" ht="18.75" spans="1:16">
@@ -17970,7 +18037,9 @@
       <c r="L46" s="118"/>
       <c r="M46" s="118"/>
       <c r="N46" s="119"/>
-      <c r="O46" s="32"/>
+      <c r="O46" s="32">
+        <v>5</v>
+      </c>
       <c r="P46" s="32"/>
     </row>
     <row r="47" ht="18.75" spans="1:16">
@@ -18034,7 +18103,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>初始年财报!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -18059,7 +18128,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>初始年财报!G8+O28</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -18082,7 +18151,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -18125,7 +18194,9 @@
       <c r="L53" s="61"/>
       <c r="M53" s="61"/>
       <c r="N53" s="62"/>
-      <c r="O53" s="130"/>
+      <c r="O53" s="130">
+        <v>3</v>
+      </c>
       <c r="P53" s="131"/>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:17">
@@ -18256,7 +18327,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="29">
         <f>初始年财报!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -18264,7 +18335,7 @@
       <c r="E59" s="86"/>
       <c r="F59" s="33">
         <f>$O$12+$O$23+$O$36+$O$44+$O$47+$O$58</f>
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G59" s="86" t="s">
         <v>125</v>
@@ -18272,28 +18343,28 @@
       <c r="H59" s="145"/>
       <c r="I59" s="146">
         <f>$M$1+$P$5+$O$10+$O$11+$O$18+$O$21+$O$22+$O$26+$O$29+$O$31+$O$33+$O$34+$O$40+$O$45+$O$46+$O$42+$O$43+$O$48+$O$53+$O$55+$O$57</f>
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="J59" s="147" t="s">
         <v>126</v>
       </c>
-      <c r="K59" s="176" t="e">
+      <c r="K59" s="176">
         <f>$O$5/$P$5</f>
-        <v>#DIV/0!</v>
+        <v>11</v>
       </c>
       <c r="L59" s="149" t="s">
         <v>127</v>
       </c>
-      <c r="M59" s="177" t="e">
+      <c r="M59" s="177">
         <f>$O$33/($O$38+$O$58)</f>
-        <v>#DIV/0!</v>
+        <v>0.363636363636364</v>
       </c>
       <c r="N59" s="151" t="s">
         <v>128</v>
       </c>
       <c r="O59" s="178">
         <f>($O$38-$O$39--$O$11-$P$5-$M$1-$O$21-$O$22--$O$29-$O$33-$O$34-$O$42-$O$45-$O$48-$O$53-$O$57+$O$58)/($O$31*7+5)*100</f>
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="P59" s="179"/>
     </row>
@@ -18304,14 +18375,14 @@
       <c r="B60" s="154"/>
       <c r="C60" s="33">
         <f>$O$11+$O$42+$O$55</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D60" s="147" t="s">
         <v>129</v>
       </c>
       <c r="E60" s="33">
         <f>$O$46-$O$47</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F60" s="155" t="s">
         <v>130</v>
@@ -18325,14 +18396,14 @@
       </c>
       <c r="I60" s="157">
         <f>'0年财报'!$C$22/'0年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'0年财报'!$C$22/'0年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.101769911504425</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -18355,28 +18426,28 @@
       </c>
       <c r="E61" s="33">
         <f>$O$27-$O$23</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F61" s="165" t="s">
         <v>134</v>
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
       </c>
-      <c r="I61" s="157" t="e">
+      <c r="I61" s="157">
         <f>'0年财报'!$C$22/'0年财报'!$C$4</f>
-        <v>#DIV/0!</v>
+        <v>-2.09090909090909</v>
       </c>
       <c r="J61" s="156" t="s">
         <v>136</v>
       </c>
-      <c r="K61" s="157" t="e">
+      <c r="K61" s="157">
         <f>1-'0年财报'!$C$5/'0年财报'!$C$4</f>
-        <v>#DIV/0!</v>
+        <v>0.636363636363636</v>
       </c>
       <c r="L61" s="160"/>
       <c r="M61" s="160"/>
@@ -18848,7 +18919,7 @@
       </c>
       <c r="C4" s="10">
         <f>'0年经营'!O38</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -18869,7 +18940,7 @@
       </c>
       <c r="C5" s="10">
         <f>'0年经营'!O39</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -18895,7 +18966,7 @@
       </c>
       <c r="G6" s="10">
         <f>初始年财报!G6+'0年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -18908,7 +18979,7 @@
       </c>
       <c r="C7" s="15">
         <f>C4-C5</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -18917,7 +18988,7 @@
       </c>
       <c r="G7" s="10">
         <f>初始年财报!G7+'0年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -18926,7 +18997,7 @@
       </c>
       <c r="K7" s="10">
         <f>'0年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -18940,7 +19011,7 @@
       </c>
       <c r="G8" s="10">
         <f>初始年财报!G8+'0年经营'!G61</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -18949,7 +19020,7 @@
       </c>
       <c r="K8" s="10">
         <f>'0年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -18963,7 +19034,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -18976,7 +19047,7 @@
       </c>
       <c r="C10" s="10">
         <f>'0年经营'!O2</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -18989,7 +19060,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -18998,7 +19069,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'0年经营'!O51</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -19029,7 +19100,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -19038,7 +19109,7 @@
       </c>
       <c r="G13" s="10">
         <f>'0年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -19072,7 +19143,9 @@
       <c r="F15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="17">
+        <v>8</v>
+      </c>
       <c r="H15" s="5" t="s">
         <v>22</v>
       </c>
@@ -19092,14 +19165,16 @@
       </c>
       <c r="C16" s="10">
         <f>'0年经营'!C60</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="17"/>
+      <c r="G16" s="17">
+        <v>6</v>
+      </c>
       <c r="H16" s="5" t="s">
         <v>22</v>
       </c>
@@ -19125,7 +19200,9 @@
       <c r="F17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="17"/>
+      <c r="G17" s="17">
+        <v>0</v>
+      </c>
       <c r="H17" s="5" t="s">
         <v>22</v>
       </c>
@@ -19135,7 +19212,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -19148,7 +19225,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -19161,7 +19238,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -19170,7 +19247,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -19179,7 +19256,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -19198,7 +19275,7 @@
       <c r="B21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="15" t="str">
+      <c r="C21" s="15">
         <f>IF((FIXED(C19*C24,0)-0)&lt;0,0,FIXED(C19*C24,0,TRUE))</f>
         <v>0</v>
       </c>
@@ -19217,7 +19294,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -19226,7 +19303,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -19235,14 +19312,16 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
       <c r="B24" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="20"/>
+      <c r="C24" s="20">
+        <v>0.25</v>
+      </c>
       <c r="D24" s="21" t="s">
         <v>139</v>
       </c>
@@ -19314,7 +19393,7 @@
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
       <c r="L1" s="28"/>
-      <c r="M1" s="29" t="str">
+      <c r="M1" s="29">
         <f>'0年财报'!C21</f>
         <v>0</v>
       </c>
@@ -19641,7 +19720,7 @@
       </c>
       <c r="P10" s="43">
         <f>'0年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -20506,22 +20585,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'0年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="0">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -20557,7 +20636,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'0年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -20711,7 +20790,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'0年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -20736,7 +20815,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'0年财报'!G8+O28</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -20759,7 +20838,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -20933,7 +21012,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'0年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -21001,14 +21080,14 @@
       </c>
       <c r="I60" s="157">
         <f>'1年财报'!$C$22/'1年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.0952380952380952</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'1年财报'!$C$22/'1年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.0192307692307692</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -21037,7 +21116,7 @@
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
@@ -21587,7 +21666,7 @@
       </c>
       <c r="G6" s="10">
         <f>'0年财报'!G6+'1年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -21609,7 +21688,7 @@
       </c>
       <c r="G7" s="10">
         <f>'0年财报'!G7+'1年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -21618,7 +21697,7 @@
       </c>
       <c r="K7" s="10">
         <f>'1年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -21632,7 +21711,7 @@
       </c>
       <c r="G8" s="10">
         <f>'0年财报'!G8+'1年经营'!G61</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -21641,7 +21720,7 @@
       </c>
       <c r="K8" s="10">
         <f>'1年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -21655,7 +21734,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -21681,7 +21760,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -21690,7 +21769,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'1年经营'!O51</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -21721,7 +21800,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -21730,7 +21809,7 @@
       </c>
       <c r="G13" s="10">
         <f>'1年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -21801,7 +21880,7 @@
       </c>
       <c r="K16" s="10">
         <f>'0年财报'!K16+'0年财报'!K17</f>
-        <v>19</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -21827,7 +21906,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -21840,7 +21919,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -21853,7 +21932,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -21862,7 +21941,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -21871,7 +21950,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -21909,7 +21988,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -21918,7 +21997,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -21927,7 +22006,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -22333,7 +22412,7 @@
       </c>
       <c r="P10" s="43">
         <f>'1年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -23198,22 +23277,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'1年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -23249,7 +23328,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'1年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -23403,7 +23482,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'1年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -23428,7 +23507,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'1年财报'!G8+O28</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -23451,7 +23530,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -23625,7 +23704,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'1年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -23693,14 +23772,14 @@
       </c>
       <c r="I60" s="157">
         <f>'2年财报'!$C$22/'2年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.0769230769230769</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'2年财报'!$C$22/'2年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.0146341463414634</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -23729,7 +23808,7 @@
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
@@ -24280,7 +24359,7 @@
       </c>
       <c r="G6" s="10">
         <f>'1年财报'!G6+'2年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -24302,7 +24381,7 @@
       </c>
       <c r="G7" s="10">
         <f>'1年财报'!G7+'2年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -24311,7 +24390,7 @@
       </c>
       <c r="K7" s="10">
         <f>'2年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -24325,7 +24404,7 @@
       </c>
       <c r="G8" s="10">
         <f>'1年财报'!G8+'2年经营'!G61</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -24334,7 +24413,7 @@
       </c>
       <c r="K8" s="10">
         <f>'2年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -24348,7 +24427,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -24374,7 +24453,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -24383,7 +24462,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'2年经营'!O51</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -24414,7 +24493,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -24423,7 +24502,7 @@
       </c>
       <c r="G13" s="10">
         <f>'2年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -24494,7 +24573,7 @@
       </c>
       <c r="K16" s="10">
         <f>'1年财报'!K16+'1年财报'!K17</f>
-        <v>19</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -24520,7 +24599,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -24533,7 +24612,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -24546,7 +24625,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -24555,7 +24634,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -24564,7 +24643,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -24602,7 +24681,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -24611,7 +24690,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -24620,7 +24699,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
@@ -25026,7 +25105,7 @@
       </c>
       <c r="P10" s="43">
         <f>'2年财报'!K7+O12-O10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
@@ -25891,22 +25970,22 @@
       <c r="F41" s="103"/>
       <c r="G41" s="104">
         <f>'2年财报'!G13-M1-P5-G10-G11+G12-G18-G21-G22+G23-G26-G29-G31-G33-G34+G36-G40-G56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H41" s="104"/>
       <c r="I41" s="40">
         <f t="shared" ref="I41:M41" si="6">G41-I10-I11+I12-I18-I21-I22+I23-I26-I29-I31-I33-I34+I36-I40-I56</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J41" s="40"/>
       <c r="K41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="L41" s="40"/>
       <c r="M41" s="40">
         <f t="shared" si="6"/>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="N41" s="40"/>
       <c r="O41" s="67" t="s">
@@ -25942,7 +26021,7 @@
       <c r="O42" s="108"/>
       <c r="P42" s="43">
         <f>'2年财报'!K8+O44-O43</f>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:16">
@@ -26096,7 +26175,7 @@
       <c r="N49" s="107"/>
       <c r="O49" s="29">
         <f>'2年财报'!G7+O27-O23</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P49" s="29"/>
     </row>
@@ -26121,7 +26200,7 @@
       <c r="N50" s="36"/>
       <c r="O50" s="29">
         <f>'2年财报'!G8+O28</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P50" s="29"/>
     </row>
@@ -26144,7 +26223,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="40" t="str">
         <f>FIXED(O50/3,0,TRUE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P51" s="40"/>
     </row>
@@ -26318,7 +26397,7 @@
       <c r="B59" s="143"/>
       <c r="C59" s="144">
         <f>'2年财报'!$G$13+$F$59-$I$59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="D59" s="86" t="s">
         <v>124</v>
@@ -26386,14 +26465,14 @@
       </c>
       <c r="I60" s="157">
         <f>'3年财报'!$C$22/'3年财报'!$K$19</f>
-        <v>0</v>
+        <v>-0.0540540540540541</v>
       </c>
       <c r="J60" s="158" t="s">
         <v>132</v>
       </c>
       <c r="K60" s="157">
         <f>'3年财报'!$C$22/'3年财报'!$G$22</f>
-        <v>0</v>
+        <v>-0.00985221674876847</v>
       </c>
       <c r="L60" s="159"/>
       <c r="M60" s="160"/>
@@ -26422,7 +26501,7 @@
       </c>
       <c r="G61" s="40">
         <f>$O$28-$O$51</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H61" s="166" t="s">
         <v>135</v>
@@ -26973,7 +27052,7 @@
       </c>
       <c r="G6" s="10">
         <f>'2年财报'!G6+'3年经营'!E60</f>
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -26995,7 +27074,7 @@
       </c>
       <c r="G7" s="10">
         <f>'2年财报'!G7+'3年经营'!E61</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -27004,7 +27083,7 @@
       </c>
       <c r="K7" s="10">
         <f>'3年经营'!P10</f>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L7" s="5"/>
     </row>
@@ -27018,7 +27097,7 @@
       </c>
       <c r="G8" s="10">
         <f>'2年财报'!G8+'3年经营'!G61</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -27027,7 +27106,7 @@
       </c>
       <c r="K8" s="10">
         <f>'3年经营'!P42</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -27041,7 +27120,7 @@
       </c>
       <c r="G9" s="14">
         <f>G5+G6+G7+G8</f>
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -27067,7 +27146,7 @@
       </c>
       <c r="K10" s="14">
         <f>K6+K7+K8</f>
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:12">
@@ -27076,7 +27155,7 @@
       </c>
       <c r="C11" s="16" t="str">
         <f>'3年经营'!O51</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -27107,7 +27186,7 @@
       </c>
       <c r="C13" s="15">
         <f>C7-C10-C11</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -27116,7 +27195,7 @@
       </c>
       <c r="G13" s="10">
         <f>'3年经营'!C59</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -27187,7 +27266,7 @@
       </c>
       <c r="K16" s="10">
         <f>'2年财报'!K16+'2年财报'!K17</f>
-        <v>19</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -27213,7 +27292,7 @@
       </c>
       <c r="K17" s="14">
         <f>C22</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -27226,7 +27305,7 @@
       </c>
       <c r="G18" s="14">
         <f>G13-C21</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -27239,7 +27318,7 @@
       </c>
       <c r="C19" s="15">
         <f>C13-C16+C17</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -27248,7 +27327,7 @@
       </c>
       <c r="G19" s="14">
         <f>SUM(G14:G18)</f>
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -27257,7 +27336,7 @@
       </c>
       <c r="K19" s="14">
         <f>K15+K16+K17</f>
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:11">
@@ -27295,7 +27374,7 @@
       </c>
       <c r="C22" s="15">
         <f>C19-C21</f>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -27304,7 +27383,7 @@
       </c>
       <c r="G22" s="14">
         <f>G9+G19</f>
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -27313,7 +27392,7 @@
       </c>
       <c r="K22" s="14">
         <f>K19+K10</f>
-        <v>89</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" ht="21.95" customHeight="1" spans="2:11">
